--- a/analysis/rent-comps/The_Kelton__Rent_Comps_High_Level.xlsx
+++ b/analysis/rent-comps/The_Kelton__Rent_Comps_High_Level.xlsx
@@ -94,7 +94,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +126,11 @@
         <fgColor rgb="00EEEFF2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF3EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -364,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -530,6 +535,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1316,82 +1324,82 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Ember Peaks at American Fork</t>
+          <t>The Yard</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>American Fork</t>
+          <t>American Fork — Adjacent</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>Elysian Living</t>
+          <t>Gregory Bird</t>
         </is>
       </c>
       <c r="E9" s="30" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="38" t="n">
-        <v>0.9344</v>
+        <v>0.8194</v>
       </c>
       <c r="H9" s="38" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="I9" s="39" t="n">
-        <v>0.125158831003812</v>
+        <v>0</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>320</v>
+        <v>216</v>
       </c>
       <c r="K9" s="31" t="inlineStr"/>
       <c r="L9" s="40" t="n"/>
       <c r="M9" s="41" t="n"/>
       <c r="N9" s="31" t="n">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="P9" s="41" t="n">
-        <v>1427</v>
+        <v>1485</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="S9" s="41" t="n">
-        <v>1652</v>
+        <v>1595</v>
       </c>
       <c r="T9" s="31" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>1351</v>
+        <v>1299</v>
       </c>
       <c r="V9" s="41" t="n">
-        <v>1921</v>
+        <v>1885</v>
       </c>
       <c r="W9" s="33" t="n">
-        <v>320</v>
+        <v>216</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="Y9" s="43" t="n">
-        <v>1574</v>
+        <v>1616</v>
       </c>
       <c r="Z9" s="44">
         <f>IF(N(X9)&gt;0,Y9/X9,"")</f>
         <v/>
       </c>
       <c r="AA9" s="43" t="n">
-        <v>1377</v>
+        <v>1616</v>
       </c>
       <c r="AB9" s="44">
         <f>IF(N(X9)&gt;0,AA9/X9,"")</f>
@@ -1404,78 +1412,78 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Meadows at American Fork</t>
+          <t>Ember Peaks at American Fork</t>
         </is>
       </c>
       <c r="C10" s="45" t="n"/>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>Brad Reynolds Construction</t>
+          <t>Elysian Living</t>
         </is>
       </c>
       <c r="E10" s="30" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F10" s="37" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.9571</v>
+        <v>0.9344</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>0.956</v>
+        <v>0.9724137931034482</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.1286880100439423</v>
+        <v>0.125158831003812</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="K10" s="31" t="inlineStr"/>
       <c r="L10" s="40" t="n"/>
       <c r="M10" s="41" t="n"/>
       <c r="N10" s="31" t="n">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>734</v>
+        <v>782</v>
       </c>
       <c r="P10" s="41" t="n">
-        <v>1366</v>
+        <v>1427</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>981</v>
+        <v>1042</v>
       </c>
       <c r="S10" s="41" t="n">
-        <v>1547</v>
+        <v>1652</v>
       </c>
       <c r="T10" s="31" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>1309</v>
+        <v>1351</v>
       </c>
       <c r="V10" s="41" t="n">
-        <v>1940</v>
+        <v>1921</v>
       </c>
       <c r="W10" s="33" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>999</v>
+        <v>951</v>
       </c>
       <c r="Y10" s="43" t="n">
-        <v>1593</v>
+        <v>1574</v>
       </c>
       <c r="Z10" s="44">
         <f>IF(N(X10)&gt;0,Y10/X10,"")</f>
         <v/>
       </c>
       <c r="AA10" s="43" t="n">
-        <v>1388</v>
+        <v>1377</v>
       </c>
       <c r="AB10" s="44">
         <f>IF(N(X10)&gt;0,AA10/X10,"")</f>
@@ -1483,85 +1491,85 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Millpond</t>
-        </is>
-      </c>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>Aldon Management</t>
-        </is>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F11" s="37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="38" t="n">
-        <v>0.9206</v>
-      </c>
-      <c r="H11" s="38" t="n">
-        <v>0.8585858585858586</v>
-      </c>
-      <c r="I11" s="39" t="n">
-        <v>0.1180124223602484</v>
-      </c>
-      <c r="J11" s="30" t="n">
-        <v>214</v>
-      </c>
-      <c r="K11" s="31" t="inlineStr"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="41" t="n"/>
-      <c r="N11" s="31" t="n">
-        <v>89</v>
-      </c>
-      <c r="O11" s="40" t="n">
-        <v>881</v>
-      </c>
-      <c r="P11" s="41" t="n">
-        <v>1312</v>
-      </c>
-      <c r="Q11" s="31" t="n">
-        <v>107</v>
-      </c>
-      <c r="R11" s="40" t="n">
-        <v>1220</v>
-      </c>
-      <c r="S11" s="41" t="n">
-        <v>1464</v>
-      </c>
-      <c r="T11" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="U11" s="40" t="n">
-        <v>1598</v>
-      </c>
-      <c r="V11" s="41" t="n">
-        <v>2036</v>
-      </c>
-      <c r="W11" s="33" t="n">
-        <v>214</v>
-      </c>
-      <c r="X11" s="42" t="n">
-        <v>1110</v>
-      </c>
-      <c r="Y11" s="43" t="n">
-        <v>1449</v>
-      </c>
-      <c r="Z11" s="44">
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>Meadows at American Fork</t>
+        </is>
+      </c>
+      <c r="C11" s="48" t="n"/>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>Brad Reynolds Construction</t>
+        </is>
+      </c>
+      <c r="E11" s="50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>0.9571</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I11" s="53" t="n">
+        <v>0.1286880100439423</v>
+      </c>
+      <c r="J11" s="50" t="n">
+        <v>350</v>
+      </c>
+      <c r="K11" s="54" t="inlineStr"/>
+      <c r="L11" s="55" t="n"/>
+      <c r="M11" s="56" t="n"/>
+      <c r="N11" s="54" t="n">
+        <v>72</v>
+      </c>
+      <c r="O11" s="55" t="n">
+        <v>734</v>
+      </c>
+      <c r="P11" s="56" t="n">
+        <v>1366</v>
+      </c>
+      <c r="Q11" s="54" t="n">
+        <v>204</v>
+      </c>
+      <c r="R11" s="55" t="n">
+        <v>981</v>
+      </c>
+      <c r="S11" s="56" t="n">
+        <v>1547</v>
+      </c>
+      <c r="T11" s="54" t="n">
+        <v>74</v>
+      </c>
+      <c r="U11" s="55" t="n">
+        <v>1309</v>
+      </c>
+      <c r="V11" s="56" t="n">
+        <v>1940</v>
+      </c>
+      <c r="W11" s="46" t="n">
+        <v>350</v>
+      </c>
+      <c r="X11" s="57" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y11" s="58" t="n">
+        <v>1593</v>
+      </c>
+      <c r="Z11" s="59">
         <f>IF(N(X11)&gt;0,Y11/X11,"")</f>
         <v/>
       </c>
-      <c r="AA11" s="43" t="n">
-        <v>1278</v>
-      </c>
-      <c r="AB11" s="44">
+      <c r="AA11" s="58" t="n">
+        <v>1388</v>
+      </c>
+      <c r="AB11" s="59">
         <f>IF(N(X11)&gt;0,AA11/X11,"")</f>
         <v/>
       </c>
@@ -1572,78 +1580,82 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Alvera at The Meadows</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="n"/>
+          <t>Millpond</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>American Fork — North</t>
+        </is>
+      </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>Gelt Inc.</t>
+          <t>Aldon Management</t>
         </is>
       </c>
       <c r="E12" s="30" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F12" s="37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.9718</v>
+        <v>0.9206</v>
       </c>
       <c r="H12" s="38" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8585858585858586</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.0186104218362283</v>
+        <v>0.1180124223602484</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="K12" s="31" t="inlineStr"/>
       <c r="L12" s="40" t="n"/>
       <c r="M12" s="41" t="n"/>
       <c r="N12" s="31" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>704</v>
+        <v>881</v>
       </c>
       <c r="P12" s="41" t="n">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="Q12" s="31" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>1030</v>
+        <v>1220</v>
       </c>
       <c r="S12" s="41" t="n">
-        <v>1670</v>
+        <v>1464</v>
       </c>
       <c r="T12" s="31" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>1258</v>
+        <v>1598</v>
       </c>
       <c r="V12" s="41" t="n">
-        <v>2050</v>
+        <v>2036</v>
       </c>
       <c r="W12" s="33" t="n">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>955</v>
+        <v>1110</v>
       </c>
       <c r="Y12" s="43" t="n">
-        <v>1612</v>
+        <v>1449</v>
       </c>
       <c r="Z12" s="44">
         <f>IF(N(X12)&gt;0,Y12/X12,"")</f>
         <v/>
       </c>
       <c r="AA12" s="43" t="n">
-        <v>1582</v>
+        <v>1278</v>
       </c>
       <c r="AB12" s="44">
         <f>IF(N(X12)&gt;0,AA12/X12,"")</f>
@@ -1656,78 +1668,78 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Parc on 5th</t>
+          <t>Alvera at The Meadows</t>
         </is>
       </c>
       <c r="C13" s="45" t="n"/>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>Wasatch Group</t>
+          <t>Gelt Inc.</t>
         </is>
       </c>
       <c r="E13" s="30" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>0.9533</v>
+        <v>0.9718</v>
       </c>
       <c r="H13" s="38" t="n">
-        <v>0.941908713692946</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>0</v>
+        <v>0.0186104218362283</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>300</v>
+        <v>142</v>
       </c>
       <c r="K13" s="31" t="inlineStr"/>
       <c r="L13" s="40" t="n"/>
       <c r="M13" s="41" t="n"/>
       <c r="N13" s="31" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>747</v>
+        <v>704</v>
       </c>
       <c r="P13" s="41" t="n">
-        <v>1408</v>
+        <v>1317</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>1121</v>
+        <v>1030</v>
       </c>
       <c r="S13" s="41" t="n">
-        <v>1896</v>
+        <v>1670</v>
       </c>
       <c r="T13" s="31" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>1440</v>
+        <v>1258</v>
       </c>
       <c r="V13" s="41" t="n">
-        <v>2314</v>
+        <v>2050</v>
       </c>
       <c r="W13" s="33" t="n">
-        <v>300</v>
+        <v>142</v>
       </c>
       <c r="X13" s="42" t="n">
-        <v>1042</v>
+        <v>955</v>
       </c>
       <c r="Y13" s="43" t="n">
-        <v>1794</v>
+        <v>1612</v>
       </c>
       <c r="Z13" s="44">
         <f>IF(N(X13)&gt;0,Y13/X13,"")</f>
         <v/>
       </c>
       <c r="AA13" s="43" t="n">
-        <v>1794</v>
+        <v>1582</v>
       </c>
       <c r="AB13" s="44">
         <f>IF(N(X13)&gt;0,AA13/X13,"")</f>
@@ -1735,175 +1747,167 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>Elevate at 620</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>FourSite Property Mgmt</t>
-        </is>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F14" s="37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G14" s="38" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="H14" s="38" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I14" s="39" t="n">
-        <v>0.025609756097561</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>338</v>
-      </c>
-      <c r="K14" s="31" t="n">
-        <v>45</v>
-      </c>
-      <c r="L14" s="40" t="n">
-        <v>632</v>
-      </c>
-      <c r="M14" s="41" t="n">
-        <v>1345</v>
-      </c>
-      <c r="N14" s="31" t="n">
-        <v>119</v>
-      </c>
-      <c r="O14" s="40" t="n">
-        <v>751</v>
-      </c>
-      <c r="P14" s="41" t="n">
-        <v>1447</v>
-      </c>
-      <c r="Q14" s="31" t="n">
-        <v>146</v>
-      </c>
-      <c r="R14" s="40" t="n">
-        <v>1029</v>
-      </c>
-      <c r="S14" s="41" t="n">
-        <v>1754</v>
-      </c>
-      <c r="T14" s="31" t="n">
-        <v>28</v>
-      </c>
-      <c r="U14" s="40" t="n">
-        <v>1654</v>
-      </c>
-      <c r="V14" s="41" t="n">
-        <v>2336</v>
-      </c>
-      <c r="W14" s="33" t="n">
-        <v>338</v>
-      </c>
-      <c r="X14" s="42" t="n">
-        <v>930</v>
-      </c>
-      <c r="Y14" s="43" t="n">
-        <v>1640</v>
-      </c>
-      <c r="Z14" s="44">
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>Lehi Tech Apartments</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="n"/>
+      <c r="D14" s="49" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>0.9601328903654485</v>
+      </c>
+      <c r="I14" s="53" t="n">
+        <v>0.08668076109936573</v>
+      </c>
+      <c r="J14" s="50" t="n">
+        <v>329</v>
+      </c>
+      <c r="K14" s="54" t="inlineStr"/>
+      <c r="L14" s="55" t="n"/>
+      <c r="M14" s="56" t="n"/>
+      <c r="N14" s="54" t="n">
+        <v>147</v>
+      </c>
+      <c r="O14" s="55" t="n">
+        <v>702</v>
+      </c>
+      <c r="P14" s="56" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Q14" s="54" t="n">
+        <v>182</v>
+      </c>
+      <c r="R14" s="55" t="n">
+        <v>1040</v>
+      </c>
+      <c r="S14" s="56" t="n">
+        <v>1527</v>
+      </c>
+      <c r="T14" s="54" t="inlineStr"/>
+      <c r="U14" s="55" t="n"/>
+      <c r="V14" s="56" t="n"/>
+      <c r="W14" s="46" t="n">
+        <v>329</v>
+      </c>
+      <c r="X14" s="57" t="n">
+        <v>889</v>
+      </c>
+      <c r="Y14" s="58" t="n">
+        <v>1419</v>
+      </c>
+      <c r="Z14" s="59">
         <f>IF(N(X14)&gt;0,Y14/X14,"")</f>
         <v/>
       </c>
-      <c r="AA14" s="43" t="n">
-        <v>1598</v>
-      </c>
-      <c r="AB14" s="44">
+      <c r="AA14" s="58" t="n">
+        <v>1296</v>
+      </c>
+      <c r="AB14" s="59">
         <f>IF(N(X14)&gt;0,AA14/X14,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="n">
+      <c r="A15" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t>Rivulet Apartments</t>
-        </is>
-      </c>
-      <c r="C15" s="48" t="n"/>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Embold</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>Lehi / Traverse Mtn</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Wasatch Group</t>
         </is>
       </c>
-      <c r="E15" s="50" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F15" s="51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G15" s="52" t="n">
-        <v>0.9365</v>
-      </c>
-      <c r="H15" s="52" t="n">
-        <v>0.8962264150943396</v>
-      </c>
-      <c r="I15" s="53" t="n">
+      <c r="E15" s="30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G15" s="38" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="H15" s="38" t="n">
+        <v>0.9329896907216495</v>
+      </c>
+      <c r="I15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="50" t="n">
-        <v>252</v>
-      </c>
-      <c r="K15" s="54" t="inlineStr"/>
-      <c r="L15" s="55" t="n"/>
-      <c r="M15" s="56" t="n"/>
-      <c r="N15" s="54" t="n">
-        <v>68</v>
-      </c>
-      <c r="O15" s="55" t="n">
-        <v>706</v>
-      </c>
-      <c r="P15" s="56" t="n">
-        <v>1399</v>
-      </c>
-      <c r="Q15" s="54" t="n">
-        <v>140</v>
-      </c>
-      <c r="R15" s="55" t="n">
-        <v>994</v>
-      </c>
-      <c r="S15" s="56" t="n">
-        <v>1733</v>
-      </c>
-      <c r="T15" s="54" t="n">
-        <v>44</v>
-      </c>
-      <c r="U15" s="55" t="n">
-        <v>1155</v>
-      </c>
-      <c r="V15" s="56" t="n">
-        <v>1923</v>
-      </c>
-      <c r="W15" s="46" t="n">
-        <v>252</v>
-      </c>
-      <c r="X15" s="57" t="n">
-        <v>945</v>
-      </c>
-      <c r="Y15" s="58" t="n">
-        <v>1676</v>
-      </c>
-      <c r="Z15" s="59">
+      <c r="J15" s="30" t="n">
+        <v>232</v>
+      </c>
+      <c r="K15" s="31" t="inlineStr"/>
+      <c r="L15" s="40" t="n"/>
+      <c r="M15" s="41" t="n"/>
+      <c r="N15" s="31" t="n">
+        <v>107</v>
+      </c>
+      <c r="O15" s="40" t="n">
+        <v>751</v>
+      </c>
+      <c r="P15" s="41" t="n">
+        <v>1514</v>
+      </c>
+      <c r="Q15" s="31" t="n">
+        <v>113</v>
+      </c>
+      <c r="R15" s="40" t="n">
+        <v>1166</v>
+      </c>
+      <c r="S15" s="41" t="n">
+        <v>1889</v>
+      </c>
+      <c r="T15" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" s="40" t="n">
+        <v>1449</v>
+      </c>
+      <c r="V15" s="41" t="n">
+        <v>2423</v>
+      </c>
+      <c r="W15" s="33" t="n">
+        <v>232</v>
+      </c>
+      <c r="X15" s="42" t="n">
+        <v>989</v>
+      </c>
+      <c r="Y15" s="43" t="n">
+        <v>1744</v>
+      </c>
+      <c r="Z15" s="44">
         <f>IF(N(X15)&gt;0,Y15/X15,"")</f>
         <v/>
       </c>
-      <c r="AA15" s="58" t="n">
-        <v>1676</v>
-      </c>
-      <c r="AB15" s="59">
+      <c r="AA15" s="43" t="n">
+        <v>1744</v>
+      </c>
+      <c r="AB15" s="44">
         <f>IF(N(X15)&gt;0,AA15/X15,"")</f>
         <v/>
       </c>
@@ -1914,82 +1918,72 @@
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>Northshore</t>
-        </is>
-      </c>
-      <c r="C16" s="60" t="inlineStr">
-        <is>
-          <t>Lehi / North County</t>
-        </is>
-      </c>
+          <t>The Vue</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="n"/>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Millburn &amp; Company</t>
+          <t>Perry Commercial</t>
         </is>
       </c>
       <c r="E16" s="30" t="n">
         <v>2022</v>
       </c>
       <c r="F16" s="37" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="G16" s="38" t="n">
-        <v>0.9435</v>
+        <v>0.9286</v>
       </c>
       <c r="H16" s="38" t="n">
-        <v>0.9632352941176471</v>
+        <v>0.9690721649484536</v>
       </c>
       <c r="I16" s="39" t="n">
-        <v>0.1145454545454545</v>
+        <v>0</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="K16" s="31" t="inlineStr"/>
       <c r="L16" s="40" t="n"/>
       <c r="M16" s="41" t="n"/>
       <c r="N16" s="31" t="n">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="P16" s="41" t="n">
-        <v>1414</v>
+        <v>1670</v>
       </c>
       <c r="Q16" s="31" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="S16" s="41" t="n">
-        <v>1670</v>
-      </c>
-      <c r="T16" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="U16" s="40" t="n">
-        <v>1352</v>
-      </c>
-      <c r="V16" s="41" t="n">
-        <v>1849</v>
-      </c>
+        <v>1964</v>
+      </c>
+      <c r="T16" s="31" t="inlineStr"/>
+      <c r="U16" s="40" t="n"/>
+      <c r="V16" s="41" t="n"/>
       <c r="W16" s="33" t="n">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>1098</v>
+        <v>984</v>
       </c>
       <c r="Y16" s="43" t="n">
-        <v>1650</v>
+        <v>1817</v>
       </c>
       <c r="Z16" s="44">
         <f>IF(N(X16)&gt;0,Y16/X16,"")</f>
         <v/>
       </c>
       <c r="AA16" s="43" t="n">
-        <v>1461</v>
+        <v>1817</v>
       </c>
       <c r="AB16" s="44">
         <f>IF(N(X16)&gt;0,AA16/X16,"")</f>
@@ -2002,78 +1996,76 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Embold</t>
+          <t>Terra Vista Lehi</t>
         </is>
       </c>
       <c r="C17" s="45" t="n"/>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>Wasatch Group</t>
+          <t>Riverbend Management</t>
         </is>
       </c>
       <c r="E17" s="30" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G17" s="38" t="n">
-        <v>0.944</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="G17" s="38" t="n"/>
       <c r="H17" s="38" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.8244514106583072</v>
       </c>
       <c r="I17" s="39" t="n">
-        <v>0</v>
+        <v>0.1540483701366983</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="K17" s="31" t="inlineStr"/>
       <c r="L17" s="40" t="n"/>
       <c r="M17" s="41" t="n"/>
       <c r="N17" s="31" t="n">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="P17" s="41" t="n">
-        <v>1514</v>
+        <v>1768</v>
       </c>
       <c r="Q17" s="31" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>1166</v>
+        <v>1036</v>
       </c>
       <c r="S17" s="41" t="n">
-        <v>1889</v>
+        <v>1975</v>
       </c>
       <c r="T17" s="31" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>1449</v>
+        <v>1365</v>
       </c>
       <c r="V17" s="41" t="n">
-        <v>2423</v>
+        <v>2437</v>
       </c>
       <c r="W17" s="33" t="n">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="X17" s="42" t="n">
-        <v>989</v>
+        <v>918</v>
       </c>
       <c r="Y17" s="43" t="n">
-        <v>1744</v>
+        <v>1902</v>
       </c>
       <c r="Z17" s="44">
         <f>IF(N(X17)&gt;0,Y17/X17,"")</f>
         <v/>
       </c>
       <c r="AA17" s="43" t="n">
-        <v>1744</v>
+        <v>1609</v>
       </c>
       <c r="AB17" s="44">
         <f>IF(N(X17)&gt;0,AA17/X17,"")</f>
@@ -2086,72 +2078,76 @@
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>The Vue</t>
-        </is>
-      </c>
-      <c r="C18" s="61" t="n"/>
+          <t>Seasons of Traverse Mountain</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="n"/>
       <c r="D18" s="36" t="inlineStr">
         <is>
-          <t>Perry Commercial</t>
+          <t>Paul Willie</t>
         </is>
       </c>
       <c r="E18" s="30" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="F18" s="37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>0.9286</v>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n">
-        <v>0.9690721649484536</v>
+        <v>0.9373040752351097</v>
       </c>
       <c r="I18" s="39" t="n">
-        <v>0</v>
+        <v>0.01786853860880666</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="K18" s="31" t="inlineStr"/>
       <c r="L18" s="40" t="n"/>
       <c r="M18" s="41" t="n"/>
       <c r="N18" s="31" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>833</v>
+        <v>709</v>
       </c>
       <c r="P18" s="41" t="n">
-        <v>1670</v>
+        <v>1362</v>
       </c>
       <c r="Q18" s="31" t="n">
-        <v>154</v>
+        <v>220</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>1136</v>
+        <v>994</v>
       </c>
       <c r="S18" s="41" t="n">
-        <v>1964</v>
-      </c>
-      <c r="T18" s="31" t="inlineStr"/>
-      <c r="U18" s="40" t="n"/>
-      <c r="V18" s="41" t="n"/>
+        <v>1639</v>
+      </c>
+      <c r="T18" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="U18" s="40" t="n">
+        <v>1185</v>
+      </c>
+      <c r="V18" s="41" t="n">
+        <v>1945</v>
+      </c>
       <c r="W18" s="33" t="n">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="X18" s="42" t="n">
-        <v>984</v>
+        <v>905</v>
       </c>
       <c r="Y18" s="43" t="n">
-        <v>1817</v>
+        <v>1567</v>
       </c>
       <c r="Z18" s="44">
         <f>IF(N(X18)&gt;0,Y18/X18,"")</f>
         <v/>
       </c>
       <c r="AA18" s="43" t="n">
-        <v>1817</v>
+        <v>1539</v>
       </c>
       <c r="AB18" s="44">
         <f>IF(N(X18)&gt;0,AA18/X18,"")</f>
@@ -2160,7 +2156,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>Comp Total / Wtd Avg</t>
         </is>
@@ -2171,106 +2167,107 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="63">
+      <c r="I19" s="64">
         <f>IFERROR(1-AA19/Y19,"")</f>
         <v/>
       </c>
-      <c r="J19" s="64">
+      <c r="J19" s="65">
         <f>SUM(J9:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="66">
         <f>SUM(K9:K18)</f>
         <v/>
       </c>
-      <c r="L19" s="66">
+      <c r="L19" s="67">
         <f>IFERROR(SUMPRODUCT(L9:L18,K9:K18)/SUMPRODUCT((L9:L18&gt;0)*K9:K18),"")</f>
         <v/>
       </c>
-      <c r="M19" s="67">
+      <c r="M19" s="68">
         <f>IFERROR(SUMPRODUCT(M9:M18,K9:K18)/SUMPRODUCT((M9:M18&gt;0)*K9:K18),"")</f>
         <v/>
       </c>
-      <c r="N19" s="65">
+      <c r="N19" s="66">
         <f>SUM(N9:N18)</f>
         <v/>
       </c>
-      <c r="O19" s="66">
+      <c r="O19" s="67">
         <f>IFERROR(SUMPRODUCT(O9:O18,N9:N18)/SUMPRODUCT((O9:O18&gt;0)*N9:N18),"")</f>
         <v/>
       </c>
-      <c r="P19" s="67">
+      <c r="P19" s="68">
         <f>IFERROR(SUMPRODUCT(P9:P18,N9:N18)/SUMPRODUCT((P9:P18&gt;0)*N9:N18),"")</f>
         <v/>
       </c>
-      <c r="Q19" s="65">
+      <c r="Q19" s="66">
         <f>SUM(Q9:Q18)</f>
         <v/>
       </c>
-      <c r="R19" s="66">
+      <c r="R19" s="67">
         <f>IFERROR(SUMPRODUCT(R9:R18,Q9:Q18)/SUMPRODUCT((R9:R18&gt;0)*Q9:Q18),"")</f>
         <v/>
       </c>
-      <c r="S19" s="67">
+      <c r="S19" s="68">
         <f>IFERROR(SUMPRODUCT(S9:S18,Q9:Q18)/SUMPRODUCT((S9:S18&gt;0)*Q9:Q18),"")</f>
         <v/>
       </c>
-      <c r="T19" s="65">
+      <c r="T19" s="66">
         <f>SUM(T9:T18)</f>
         <v/>
       </c>
-      <c r="U19" s="66">
+      <c r="U19" s="67">
         <f>IFERROR(SUMPRODUCT(U9:U18,T9:T18)/SUMPRODUCT((U9:U18&gt;0)*T9:T18),"")</f>
         <v/>
       </c>
-      <c r="V19" s="67">
+      <c r="V19" s="68">
         <f>IFERROR(SUMPRODUCT(V9:V18,T9:T18)/SUMPRODUCT((V9:V18&gt;0)*T9:T18),"")</f>
         <v/>
       </c>
-      <c r="W19" s="64">
+      <c r="W19" s="65">
         <f>SUM(W9:W18)</f>
         <v/>
       </c>
-      <c r="X19" s="68">
+      <c r="X19" s="69">
         <f>IFERROR(SUMPRODUCT(X9:X18,W9:W18)/SUM(W9:W18),"")</f>
         <v/>
       </c>
-      <c r="Y19" s="69">
+      <c r="Y19" s="70">
         <f>IFERROR(SUMPRODUCT(Y9:Y18,W9:W18)/SUM(W9:W18),"")</f>
         <v/>
       </c>
-      <c r="Z19" s="70">
+      <c r="Z19" s="71">
         <f>IF(N(X19)&gt;0,Y19/X19,"")</f>
         <v/>
       </c>
-      <c r="AA19" s="69">
+      <c r="AA19" s="70">
         <f>IFERROR(SUMPRODUCT(AA9:AA18,W9:W18)/SUM(W9:W18),"")</f>
         <v/>
       </c>
-      <c r="AB19" s="70">
+      <c r="AB19" s="71">
         <f>IF(N(X19)&gt;0,AA19/X19,"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="71" t="inlineStr">
-        <is>
-          <t>Rent &amp; total-PSF columns are color-scaled down each column across the comps (pale red = lower, pale blue = higher; subject = cream, excluded). Rent (by bedroom) = HelloData T90-day executed asking (market) rent on leases that went off-market 14 Apr–13 Jul 2026; Total–Effective = HelloData effective (net of concessions); Conc = 1 − Eff ÷ Gross. SF (by bedroom &amp; total) = CoStar avg SF by unit type; subject SF/counts = subject rent roll. Comp unit counts = CoStar; Occ % = CoStar occupied (1 − vacancy); Leased % = HelloData. Comps grouped by submarket cluster: American Fork (subject submarket) vs Lehi / North County. PSF = total rent ÷ total SF.</t>
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t>Rent &amp; total-PSF columns are color-scaled down each column across the comps (pale red = lower, pale blue = higher; subject = cream, excluded). Rent (by bedroom) = HelloData T90-day executed asking (market) rent on leases off-market 14 Apr–13 Jul 2026; Total–Effective = HelloData effective (net of concessions); Conc = 1 − Eff ÷ Gross. SF (by bedroom &amp; total) = CoStar avg SF by unit type; subject SF/counts = subject rent roll; comp unit counts = CoStar. Occ % = CoStar occupied (1 − vacancy); Leased % = HelloData. Clusters: American Fork — Adjacent (right next to the subject) · American Fork — North · Lehi / Traverse Mountain. The Yard &amp; Terra Vista are in initial lease-up; Terra Vista &amp; Seasons sit ~5 mi north (outside the 5-mi CoStar pull) so identity/SF/counts come from the TMG Seasons model (CoStar-sourced) and they carry no CoStar occupancy (Leased %-HD shown). Seasons is shown apartment-only (440 units); the adjacent Seasons townhomes on its website are excluded. PSF = total rent ÷ total SF.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C9:C15"/>
+  <mergeCells count="12">
+    <mergeCell ref="A21:AB21"/>
     <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A21:AB21"/>
+    <mergeCell ref="C12:C14"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="C16:C18"/>
     <mergeCell ref="Q4:S4"/>
     <mergeCell ref="T4:V4"/>
     <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="N4:P4"/>
+    <mergeCell ref="C15:C18"/>
     <mergeCell ref="AA4:AB4"/>
   </mergeCells>
   <conditionalFormatting sqref="M9:M18">

--- a/analysis/rent-comps/The_Kelton__Rent_Comps_High_Level.xlsx
+++ b/analysis/rent-comps/The_Kelton__Rent_Comps_High_Level.xlsx
@@ -1222,32 +1222,41 @@
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="21" t="n"/>
       <c r="M6" s="22" t="n"/>
-      <c r="N6" s="20" t="n">
-        <v>84</v>
-      </c>
-      <c r="O6" s="21" t="n">
-        <v>744</v>
-      </c>
-      <c r="P6" s="22" t="n">
-        <v>1432</v>
-      </c>
-      <c r="Q6" s="20" t="n">
-        <v>132</v>
-      </c>
-      <c r="R6" s="21" t="n">
-        <v>1057</v>
-      </c>
-      <c r="S6" s="22" t="n">
-        <v>1639</v>
-      </c>
-      <c r="T6" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="U6" s="21" t="n">
-        <v>1311</v>
-      </c>
-      <c r="V6" s="22" t="n">
-        <v>1928</v>
+      <c r="N6" s="20">
+        <f>SUMIFS(Assumptions!$F$50:$F$54,Assumptions!$C$50:$C$54,1)</f>
+        <v/>
+      </c>
+      <c r="O6" s="21">
+        <f t="array" ref="O6">SUMPRODUCT((Assumptions!$C$50:$C$54=1)*Assumptions!$F$50:$F$54*Assumptions!$H$50:$H$54)/N6</f>
+        <v/>
+      </c>
+      <c r="P6" s="22">
+        <f t="array" ref="P6">SUMPRODUCT((Assumptions!$C$50:$C$54=1)*Assumptions!$F$50:$F$54*Assumptions!$M$50:$M$54)/N6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="20">
+        <f>SUMIFS(Assumptions!$F$50:$F$54,Assumptions!$C$50:$C$54,2)</f>
+        <v/>
+      </c>
+      <c r="R6" s="21">
+        <f t="array" ref="R6">SUMPRODUCT((Assumptions!$C$50:$C$54=2)*Assumptions!$F$50:$F$54*Assumptions!$H$50:$H$54)/Q6</f>
+        <v/>
+      </c>
+      <c r="S6" s="22">
+        <f t="array" ref="S6">SUMPRODUCT((Assumptions!$C$50:$C$54=2)*Assumptions!$F$50:$F$54*Assumptions!$M$50:$M$54)/Q6</f>
+        <v/>
+      </c>
+      <c r="T6" s="20">
+        <f>SUMIFS(Assumptions!$F$50:$F$54,Assumptions!$C$50:$C$54,3)</f>
+        <v/>
+      </c>
+      <c r="U6" s="21">
+        <f t="array" ref="U6">SUMPRODUCT((Assumptions!$C$50:$C$54=3)*Assumptions!$F$50:$F$54*Assumptions!$H$50:$H$54)/T6</f>
+        <v/>
+      </c>
+      <c r="V6" s="22">
+        <f t="array" ref="V6">SUMPRODUCT((Assumptions!$C$50:$C$54=3)*Assumptions!$F$50:$F$54*Assumptions!$M$50:$M$54)/T6</f>
+        <v/>
       </c>
       <c r="W6" s="12" t="n">
         <v>240</v>
@@ -1255,15 +1264,17 @@
       <c r="X6" s="23" t="n">
         <v>972</v>
       </c>
-      <c r="Y6" s="24" t="n">
-        <v>1595</v>
+      <c r="Y6" s="24">
+        <f>((N6*P6)+(Q6*S6)+(T6*V6))/W6</f>
+        <v/>
       </c>
       <c r="Z6" s="25">
         <f>IF(N(X6)&gt;0,Y6/X6,"")</f>
         <v/>
       </c>
-      <c r="AA6" s="24" t="n">
-        <v>1502</v>
+      <c r="AA6" s="24">
+        <f>'Cash Flow (Annual)'!K5</f>
+        <v/>
       </c>
       <c r="AB6" s="25">
         <f>IF(N(X6)&gt;0,AA6/X6,"")</f>
@@ -1368,7 +1379,7 @@
         <v>1485</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="R9" s="40" t="n">
         <v>1022</v>
@@ -1377,7 +1388,7 @@
         <v>1595</v>
       </c>
       <c r="T9" s="31" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="U9" s="40" t="n">
         <v>1299</v>
@@ -1389,17 +1400,17 @@
         <v>216</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>969</v>
+        <v>929</v>
       </c>
       <c r="Y9" s="43" t="n">
-        <v>1616</v>
+        <v>1574</v>
       </c>
       <c r="Z9" s="44">
         <f>IF(N(X9)&gt;0,Y9/X9,"")</f>
         <v/>
       </c>
       <c r="AA9" s="43" t="n">
-        <v>1616</v>
+        <v>1574</v>
       </c>
       <c r="AB9" s="44">
         <f>IF(N(X9)&gt;0,AA9/X9,"")</f>
